--- a/resources/digital-products/files/dp-basics-traffic-log.xlsx
+++ b/resources/digital-products/files/dp-basics-traffic-log.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="12">
@@ -520,7 +520,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Fortnight traffic log</t>
+          <t>Two-week traffic log</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -559,7 +559,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Kept per sale (£)</t>
+          <t>Kept per sale ($)</t>
         </is>
       </c>
       <c r="B5" s="6" t="n">
@@ -594,7 +594,7 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Revenue (£)</t>
+          <t>Revenue ($)</t>
         </is>
       </c>
     </row>
@@ -890,7 +890,7 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Revenue per visitor (£)</t>
+          <t>Revenue per visitor ($)</t>
         </is>
       </c>
       <c r="B23" s="15">
@@ -922,5 +922,6 @@
     <mergeCell ref="A26:C26"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
--- a/resources/digital-products/files/dp-basics-traffic-log.xlsx
+++ b/resources/digital-products/files/dp-basics-traffic-log.xlsx
@@ -522,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -556,6 +556,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
@@ -571,6 +572,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
@@ -898,6 +900,7 @@
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="16" t="n"/>
       <c r="B25" s="16" t="n"/>
@@ -910,12 +913,17 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
-        </is>
-      </c>
+          <t>ePORTS — your ecom source (eports.global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
